--- a/record-linkage-of-ofac-and-eu-sanctions-lists/text-embeddings/text_embeddings_confusion_matrix_process_measures.xlsx
+++ b/record-linkage-of-ofac-and-eu-sanctions-lists/text-embeddings/text_embeddings_confusion_matrix_process_measures.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9778581999999005</v>
+        <v>0.991237899987027</v>
       </c>
       <c r="C2" t="n">
-        <v>233.90234375</v>
+        <v>236.06640625</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.348956400004681</v>
+        <v>4.635497900017072</v>
       </c>
       <c r="C3" t="n">
-        <v>43.046875</v>
+        <v>489.5703125</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4079434000013862</v>
+        <v>1.187977599969599</v>
       </c>
       <c r="C4" t="n">
-        <v>7.27734375</v>
+        <v>-234.99609375</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2726279000053182</v>
+        <v>0.7697735000401735</v>
       </c>
       <c r="C5" t="n">
-        <v>3.41796875</v>
+        <v>1.23828125</v>
       </c>
     </row>
   </sheetData>
